--- a/experiment_realbug/human_kappa/rating_sheet_TEMPLATE.xlsx
+++ b/experiment_realbug/human_kappa/rating_sheet_TEMPLATE.xlsx
@@ -420,16 +420,17 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:G37"/>
+  <dimension ref="A1:H37"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="7" customWidth="1" min="1" max="1"/>
     <col width="22" customWidth="1" min="2" max="2"/>
-    <col width="20" customWidth="1" min="3" max="3"/>
-    <col width="46" customWidth="1" min="4" max="4"/>
-    <col width="40" customWidth="1" min="5" max="5"/>
-    <col width="11" customWidth="1" min="6" max="6"/>
-    <col width="22" customWidth="1" min="7" max="7"/>
+    <col width="40" customWidth="1" min="3" max="3"/>
+    <col width="18" customWidth="1" min="4" max="4"/>
+    <col width="44" customWidth="1" min="5" max="5"/>
+    <col width="38" customWidth="1" min="6" max="6"/>
+    <col width="11" customWidth="1" min="7" max="7"/>
+    <col width="22" customWidth="1" min="8" max="8"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -445,25 +446,30 @@
       </c>
       <c r="C1" s="1" t="inlineStr">
         <is>
+          <t>program (what it computes)</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
           <t>mr_name</t>
         </is>
       </c>
-      <c r="D1" s="1" t="inlineStr">
+      <c r="E1" s="1" t="inlineStr">
         <is>
           <t>JIR (input relation)</t>
         </is>
       </c>
-      <c r="E1" s="1" t="inlineStr">
+      <c r="F1" s="1" t="inlineStr">
         <is>
           <t>JOR (output relation)</t>
         </is>
       </c>
-      <c r="F1" s="1" t="inlineStr">
+      <c r="G1" s="1" t="inlineStr">
         <is>
           <t>category</t>
         </is>
       </c>
-      <c r="G1" s="1" t="inlineStr">
+      <c r="H1" s="1" t="inlineStr">
         <is>
           <t>notes</t>
         </is>
@@ -482,21 +488,26 @@
       </c>
       <c r="C2" s="2" t="inlineStr">
         <is>
+          <t>add(other): complex addition; out = this + other (real and imaginary parts added separately). Operands this=(this.re,this.im), other=(other.re,other.im); result out=(out.re,out.im).</t>
+        </is>
+      </c>
+      <c r="D2" s="2" t="inlineStr">
+        <is>
           <t>G_swap_negate</t>
         </is>
       </c>
-      <c r="D2" s="2" t="inlineStr">
+      <c r="E2" s="2" t="inlineStr">
         <is>
           <t>(this.re1 ~= other.re2)  AND  (this.im1 ~= other.im2)  AND  (other.re1 ~= this.re2)  AND  (other.im1 ~= this.im2)</t>
         </is>
       </c>
-      <c r="E2" s="2" t="inlineStr">
+      <c r="F2" s="2" t="inlineStr">
         <is>
           <t>(out.re1 ~= out.re2)  AND  (out.im1 ~= out.im2)</t>
         </is>
       </c>
-      <c r="F2" s="2" t="inlineStr"/>
       <c r="G2" s="2" t="inlineStr"/>
+      <c r="H2" s="2" t="inlineStr"/>
     </row>
     <row r="3">
       <c r="A3" s="2" t="inlineStr">
@@ -511,21 +522,26 @@
       </c>
       <c r="C3" s="2" t="inlineStr">
         <is>
+          <t>add(other): complex addition; out = this + other (real and imaginary parts added separately). Operands this=(this.re,this.im), other=(other.re,other.im); result out=(out.re,out.im).</t>
+        </is>
+      </c>
+      <c r="D3" s="2" t="inlineStr">
+        <is>
           <t>L_scale</t>
         </is>
       </c>
-      <c r="D3" s="2" t="inlineStr">
+      <c r="E3" s="2" t="inlineStr">
         <is>
           <t>(this.re1 ~= 2.0·this.re2)  AND  (this.im1 ~= 2.0·this.im2)  AND  (other.re1 ~= 2.0·other.re2)  AND  (other.im1 ~= 2.0·other.im2)</t>
         </is>
       </c>
-      <c r="E3" s="2" t="inlineStr">
+      <c r="F3" s="2" t="inlineStr">
         <is>
           <t>(out.re1 ~= 2.0·out.re2)  AND  (out.im1 ~= 2.0·out.im2)</t>
         </is>
       </c>
-      <c r="F3" s="2" t="inlineStr"/>
       <c r="G3" s="2" t="inlineStr"/>
+      <c r="H3" s="2" t="inlineStr"/>
     </row>
     <row r="4">
       <c r="A4" s="2" t="inlineStr">
@@ -540,21 +556,26 @@
       </c>
       <c r="C4" s="2" t="inlineStr">
         <is>
+          <t>add(other): complex addition; out = this + other (real and imaginary parts added separately). Operands this=(this.re,this.im), other=(other.re,other.im); result out=(out.re,out.im).</t>
+        </is>
+      </c>
+      <c r="D4" s="2" t="inlineStr">
+        <is>
           <t>T_shift_re</t>
         </is>
       </c>
-      <c r="D4" s="2" t="inlineStr">
+      <c r="E4" s="2" t="inlineStr">
         <is>
           <t>((this.re1 ~= (this.re2 + 1.0)))  AND  (this.im1 ~= this.im2)  AND  (other.re1 ~= other.re2)  AND  (other.im1 ~= other.im2)</t>
         </is>
       </c>
-      <c r="E4" s="2" t="inlineStr">
+      <c r="F4" s="2" t="inlineStr">
         <is>
           <t>((out.re1 ~= (out.re2 + 1.0)))  AND  (out.im1 ~= out.im2)</t>
         </is>
       </c>
-      <c r="F4" s="2" t="inlineStr"/>
       <c r="G4" s="2" t="inlineStr"/>
+      <c r="H4" s="2" t="inlineStr"/>
     </row>
     <row r="5">
       <c r="A5" s="2" t="inlineStr">
@@ -569,21 +590,26 @@
       </c>
       <c r="C5" s="2" t="inlineStr">
         <is>
+          <t>clamp(lo, hi, x): clamp x into the interval [lo, hi]; returns min(max(x, lo), hi).</t>
+        </is>
+      </c>
+      <c r="D5" s="2" t="inlineStr">
+        <is>
           <t>G_negate_bound_swap</t>
         </is>
       </c>
-      <c r="D5" s="2" t="inlineStr">
+      <c r="E5" s="2" t="inlineStr">
         <is>
           <t>((lo1 ~= (-hi2)))  AND  ((hi1 ~= (-lo2)))  AND  ((x1 ~= (-x2)))</t>
         </is>
       </c>
-      <c r="E5" s="2" t="inlineStr">
+      <c r="F5" s="2" t="inlineStr">
         <is>
           <t>out1 ~= (-out2)</t>
         </is>
       </c>
-      <c r="F5" s="2" t="inlineStr"/>
       <c r="G5" s="2" t="inlineStr"/>
+      <c r="H5" s="2" t="inlineStr"/>
     </row>
     <row r="6">
       <c r="A6" s="2" t="inlineStr">
@@ -598,21 +624,26 @@
       </c>
       <c r="C6" s="2" t="inlineStr">
         <is>
+          <t>clamp(lo, hi, x): clamp x into the interval [lo, hi]; returns min(max(x, lo), hi).</t>
+        </is>
+      </c>
+      <c r="D6" s="2" t="inlineStr">
+        <is>
           <t>L_scale</t>
         </is>
       </c>
-      <c r="D6" s="2" t="inlineStr">
+      <c r="E6" s="2" t="inlineStr">
         <is>
           <t>(lo1 ~= 2.0·lo2)  AND  (hi1 ~= 2.0·hi2)  AND  (x1 ~= 2.0·x2)</t>
         </is>
       </c>
-      <c r="E6" s="2" t="inlineStr">
+      <c r="F6" s="2" t="inlineStr">
         <is>
           <t>out1 ~= 2.0·out2</t>
         </is>
       </c>
-      <c r="F6" s="2" t="inlineStr"/>
       <c r="G6" s="2" t="inlineStr"/>
+      <c r="H6" s="2" t="inlineStr"/>
     </row>
     <row r="7">
       <c r="A7" s="2" t="inlineStr">
@@ -627,21 +658,26 @@
       </c>
       <c r="C7" s="2" t="inlineStr">
         <is>
+          <t>clamp(lo, hi, x): clamp x into the interval [lo, hi]; returns min(max(x, lo), hi).</t>
+        </is>
+      </c>
+      <c r="D7" s="2" t="inlineStr">
+        <is>
           <t>O_le_mono_in_x</t>
         </is>
       </c>
-      <c r="D7" s="2" t="inlineStr">
+      <c r="E7" s="2" t="inlineStr">
         <is>
           <t>(lo2 ~= lo1)  AND  (hi2 ~= hi1)  AND  (x2 &lt;= x1)</t>
         </is>
       </c>
-      <c r="E7" s="2" t="inlineStr">
+      <c r="F7" s="2" t="inlineStr">
         <is>
           <t>out2 &lt;= out1</t>
         </is>
       </c>
-      <c r="F7" s="2" t="inlineStr"/>
       <c r="G7" s="2" t="inlineStr"/>
+      <c r="H7" s="2" t="inlineStr"/>
     </row>
     <row r="8">
       <c r="A8" s="2" t="inlineStr">
@@ -656,21 +692,26 @@
       </c>
       <c r="C8" s="2" t="inlineStr">
         <is>
+          <t>clamp(lo, hi, x): clamp x into the interval [lo, hi]; returns min(max(x, lo), hi).</t>
+        </is>
+      </c>
+      <c r="D8" s="2" t="inlineStr">
+        <is>
           <t>T_shift</t>
         </is>
       </c>
-      <c r="D8" s="2" t="inlineStr">
+      <c r="E8" s="2" t="inlineStr">
         <is>
           <t>((lo1 ~= (lo2 + 1.0)))  AND  ((hi1 ~= (hi2 + 1.0)))  AND  ((x1 ~= (x2 + 1.0)))</t>
         </is>
       </c>
-      <c r="E8" s="2" t="inlineStr">
+      <c r="F8" s="2" t="inlineStr">
         <is>
           <t>out1 ~= (out2 + 1.0)</t>
         </is>
       </c>
-      <c r="F8" s="2" t="inlineStr"/>
       <c r="G8" s="2" t="inlineStr"/>
+      <c r="H8" s="2" t="inlineStr"/>
     </row>
     <row r="9">
       <c r="A9" s="2" t="inlineStr">
@@ -685,21 +726,26 @@
       </c>
       <c r="C9" s="2" t="inlineStr">
         <is>
+          <t>exactLog2(n): base-2 logarithm of a positive integer n (so exactLog2(2*n) = exactLog2(n) + 1).</t>
+        </is>
+      </c>
+      <c r="D9" s="2" t="inlineStr">
+        <is>
           <t>L_idem_at_one</t>
         </is>
       </c>
-      <c r="D9" s="2" t="inlineStr">
+      <c r="E9" s="2" t="inlineStr">
         <is>
           <t>n1 = 2·n2</t>
         </is>
       </c>
-      <c r="E9" s="2" t="inlineStr">
+      <c r="F9" s="2" t="inlineStr">
         <is>
           <t>out1 = (out2 + 1)</t>
         </is>
       </c>
-      <c r="F9" s="2" t="inlineStr"/>
       <c r="G9" s="2" t="inlineStr"/>
+      <c r="H9" s="2" t="inlineStr"/>
     </row>
     <row r="10">
       <c r="A10" s="2" t="inlineStr">
@@ -714,21 +760,26 @@
       </c>
       <c r="C10" s="2" t="inlineStr">
         <is>
+          <t>exactLog2(n): base-2 logarithm of a positive integer n (so exactLog2(2*n) = exactLog2(n) + 1).</t>
+        </is>
+      </c>
+      <c r="D10" s="2" t="inlineStr">
+        <is>
           <t>O_le_monotone</t>
         </is>
       </c>
-      <c r="D10" s="2" t="inlineStr">
+      <c r="E10" s="2" t="inlineStr">
         <is>
           <t>n2 &gt; 0  AND  (n2 &amp; (n2 - 1)) = 0  AND  n1 &gt; 0  AND  (n1 &amp; (n1 - 1)) = 0  AND  n2 &lt;= n1</t>
         </is>
       </c>
-      <c r="E10" s="2" t="inlineStr">
+      <c r="F10" s="2" t="inlineStr">
         <is>
           <t>out2 &lt;= out1</t>
         </is>
       </c>
-      <c r="F10" s="2" t="inlineStr"/>
       <c r="G10" s="2" t="inlineStr"/>
+      <c r="H10" s="2" t="inlineStr"/>
     </row>
     <row r="11">
       <c r="A11" s="2" t="inlineStr">
@@ -743,21 +794,26 @@
       </c>
       <c r="C11" s="2" t="inlineStr">
         <is>
+          <t>exactLog2(n): base-2 logarithm of a positive integer n (so exactLog2(2*n) = exactLog2(n) + 1).</t>
+        </is>
+      </c>
+      <c r="D11" s="2" t="inlineStr">
+        <is>
           <t>T_double</t>
         </is>
       </c>
-      <c r="D11" s="2" t="inlineStr">
+      <c r="E11" s="2" t="inlineStr">
         <is>
           <t>n1 ~= 2.0·n2</t>
         </is>
       </c>
-      <c r="E11" s="2" t="inlineStr">
+      <c r="F11" s="2" t="inlineStr">
         <is>
           <t>out1 ~= (out2 + 1.0)</t>
         </is>
       </c>
-      <c r="F11" s="2" t="inlineStr"/>
       <c r="G11" s="2" t="inlineStr"/>
+      <c r="H11" s="2" t="inlineStr"/>
     </row>
     <row r="12">
       <c r="A12" s="2" t="inlineStr">
@@ -772,21 +828,26 @@
       </c>
       <c r="C12" s="2" t="inlineStr">
         <is>
+          <t>gcdSig(a, b): greatest common divisor of |a| and |b| (inputs sign-normalised, then Euclidean gcd).</t>
+        </is>
+      </c>
+      <c r="D12" s="2" t="inlineStr">
+        <is>
           <t>G_swap_negate</t>
         </is>
       </c>
-      <c r="D12" s="2" t="inlineStr">
+      <c r="E12" s="2" t="inlineStr">
         <is>
           <t>(a1 = b2)  AND  (b1 = a2)</t>
         </is>
       </c>
-      <c r="E12" s="2" t="inlineStr">
+      <c r="F12" s="2" t="inlineStr">
         <is>
           <t>out1 = out2</t>
         </is>
       </c>
-      <c r="F12" s="2" t="inlineStr"/>
       <c r="G12" s="2" t="inlineStr"/>
+      <c r="H12" s="2" t="inlineStr"/>
     </row>
     <row r="13">
       <c r="A13" s="2" t="inlineStr">
@@ -801,21 +862,26 @@
       </c>
       <c r="C13" s="2" t="inlineStr">
         <is>
+          <t>gcdSig(a, b): greatest common divisor of |a| and |b| (inputs sign-normalised, then Euclidean gcd).</t>
+        </is>
+      </c>
+      <c r="D13" s="2" t="inlineStr">
+        <is>
           <t>L_scale</t>
         </is>
       </c>
-      <c r="D13" s="2" t="inlineStr">
+      <c r="E13" s="2" t="inlineStr">
         <is>
           <t>a1 = 2L·a2  AND  b1 = 2L·b2</t>
         </is>
       </c>
-      <c r="E13" s="2" t="inlineStr">
+      <c r="F13" s="2" t="inlineStr">
         <is>
           <t>out1 = 2L·out2</t>
         </is>
       </c>
-      <c r="F13" s="2" t="inlineStr"/>
       <c r="G13" s="2" t="inlineStr"/>
+      <c r="H13" s="2" t="inlineStr"/>
     </row>
     <row r="14">
       <c r="A14" s="2" t="inlineStr">
@@ -830,21 +896,26 @@
       </c>
       <c r="C14" s="2" t="inlineStr">
         <is>
+          <t>hypotSig(a, b): Euclidean hypotenuse, sqrt(a^2 + b^2).</t>
+        </is>
+      </c>
+      <c r="D14" s="2" t="inlineStr">
+        <is>
           <t>G_swap_negate</t>
         </is>
       </c>
-      <c r="D14" s="2" t="inlineStr">
+      <c r="E14" s="2" t="inlineStr">
         <is>
           <t>(a1 ~= b2)  AND  (b1 ~= a2)</t>
         </is>
       </c>
-      <c r="E14" s="2" t="inlineStr">
+      <c r="F14" s="2" t="inlineStr">
         <is>
           <t>out1 ~= out2</t>
         </is>
       </c>
-      <c r="F14" s="2" t="inlineStr"/>
       <c r="G14" s="2" t="inlineStr"/>
+      <c r="H14" s="2" t="inlineStr"/>
     </row>
     <row r="15">
       <c r="A15" s="2" t="inlineStr">
@@ -859,21 +930,26 @@
       </c>
       <c r="C15" s="2" t="inlineStr">
         <is>
+          <t>hypotSig(a, b): Euclidean hypotenuse, sqrt(a^2 + b^2).</t>
+        </is>
+      </c>
+      <c r="D15" s="2" t="inlineStr">
+        <is>
           <t>L_scale</t>
         </is>
       </c>
-      <c r="D15" s="2" t="inlineStr">
+      <c r="E15" s="2" t="inlineStr">
         <is>
           <t>(a1 ~= 2.0·a2)  AND  (b1 ~= 2.0·b2)</t>
         </is>
       </c>
-      <c r="E15" s="2" t="inlineStr">
+      <c r="F15" s="2" t="inlineStr">
         <is>
           <t>out1 ~= 2.0·out2</t>
         </is>
       </c>
-      <c r="F15" s="2" t="inlineStr"/>
       <c r="G15" s="2" t="inlineStr"/>
+      <c r="H15" s="2" t="inlineStr"/>
     </row>
     <row r="16">
       <c r="A16" s="2" t="inlineStr">
@@ -888,21 +964,26 @@
       </c>
       <c r="C16" s="2" t="inlineStr">
         <is>
+          <t>hypotSig(a, b): Euclidean hypotenuse, sqrt(a^2 + b^2).</t>
+        </is>
+      </c>
+      <c r="D16" s="2" t="inlineStr">
+        <is>
           <t>O_le_mono_in_abs</t>
         </is>
       </c>
-      <c r="D16" s="2" t="inlineStr">
+      <c r="E16" s="2" t="inlineStr">
         <is>
           <t>(|a2| &lt;= |a1|)  AND  (b2 ~= b1)</t>
         </is>
       </c>
-      <c r="E16" s="2" t="inlineStr">
+      <c r="F16" s="2" t="inlineStr">
         <is>
           <t>out2 &lt;= out1</t>
         </is>
       </c>
-      <c r="F16" s="2" t="inlineStr"/>
       <c r="G16" s="2" t="inlineStr"/>
+      <c r="H16" s="2" t="inlineStr"/>
     </row>
     <row r="17">
       <c r="A17" s="2" t="inlineStr">
@@ -917,21 +998,26 @@
       </c>
       <c r="C17" s="2" t="inlineStr">
         <is>
+          <t>isSequence(a, b, c): returns true iff a, b, c form an arithmetic sequence (b - a == c - b).</t>
+        </is>
+      </c>
+      <c r="D17" s="2" t="inlineStr">
+        <is>
           <t>B_rel_xor_reverse</t>
         </is>
       </c>
-      <c r="D17" s="2" t="inlineStr">
+      <c r="E17" s="2" t="inlineStr">
         <is>
           <t>(a1 ~= c2)  AND  (b1 ~= b2)  AND  (c1 ~= a2)</t>
         </is>
       </c>
-      <c r="E17" s="2" t="inlineStr">
+      <c r="F17" s="2" t="inlineStr">
         <is>
           <t>!(out2  AND  out1)</t>
         </is>
       </c>
-      <c r="F17" s="2" t="inlineStr"/>
       <c r="G17" s="2" t="inlineStr"/>
+      <c r="H17" s="2" t="inlineStr"/>
     </row>
     <row r="18">
       <c r="A18" s="2" t="inlineStr">
@@ -946,21 +1032,26 @@
       </c>
       <c r="C18" s="2" t="inlineStr">
         <is>
+          <t>isSequence(a, b, c): returns true iff a, b, c form an arithmetic sequence (b - a == c - b).</t>
+        </is>
+      </c>
+      <c r="D18" s="2" t="inlineStr">
+        <is>
           <t>G_negate_reverse</t>
         </is>
       </c>
-      <c r="D18" s="2" t="inlineStr">
+      <c r="E18" s="2" t="inlineStr">
         <is>
           <t>((a1 ~= (-c2)))  AND  ((b1 ~= (-b2)))  AND  ((c1 ~= (-a2)))</t>
         </is>
       </c>
-      <c r="E18" s="2" t="inlineStr">
+      <c r="F18" s="2" t="inlineStr">
         <is>
           <t>out1 = out2</t>
         </is>
       </c>
-      <c r="F18" s="2" t="inlineStr"/>
       <c r="G18" s="2" t="inlineStr"/>
+      <c r="H18" s="2" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" s="2" t="inlineStr">
@@ -975,21 +1066,26 @@
       </c>
       <c r="C19" s="2" t="inlineStr">
         <is>
+          <t>isSequence(a, b, c): returns true iff a, b, c form an arithmetic sequence (b - a == c - b).</t>
+        </is>
+      </c>
+      <c r="D19" s="2" t="inlineStr">
+        <is>
           <t>L_scale_pos</t>
         </is>
       </c>
-      <c r="D19" s="2" t="inlineStr">
+      <c r="E19" s="2" t="inlineStr">
         <is>
           <t>(a1 ~= 2.0·a2)  AND  (b1 ~= 2.0·b2)  AND  (c1 ~= 2.0·c2)</t>
         </is>
       </c>
-      <c r="E19" s="2" t="inlineStr">
+      <c r="F19" s="2" t="inlineStr">
         <is>
           <t>out1 = out2</t>
         </is>
       </c>
-      <c r="F19" s="2" t="inlineStr"/>
       <c r="G19" s="2" t="inlineStr"/>
+      <c r="H19" s="2" t="inlineStr"/>
     </row>
     <row r="20">
       <c r="A20" s="2" t="inlineStr">
@@ -1004,21 +1100,26 @@
       </c>
       <c r="C20" s="2" t="inlineStr">
         <is>
+          <t>isSequence(a, b, c): returns true iff a, b, c form an arithmetic sequence (b - a == c - b).</t>
+        </is>
+      </c>
+      <c r="D20" s="2" t="inlineStr">
+        <is>
           <t>O_le_transitivity</t>
         </is>
       </c>
-      <c r="D20" s="2" t="inlineStr">
+      <c r="E20" s="2" t="inlineStr">
         <is>
           <t>(a1 &lt;= a2)  AND  (b2 &lt;= b1)  AND  (c2 &lt;= c1)</t>
         </is>
       </c>
-      <c r="E20" s="2" t="inlineStr">
+      <c r="F20" s="2" t="inlineStr">
         <is>
           <t>(!out2)  OR  out1</t>
         </is>
       </c>
-      <c r="F20" s="2" t="inlineStr"/>
       <c r="G20" s="2" t="inlineStr"/>
+      <c r="H20" s="2" t="inlineStr"/>
     </row>
     <row r="21">
       <c r="A21" s="2" t="inlineStr">
@@ -1033,21 +1134,26 @@
       </c>
       <c r="C21" s="2" t="inlineStr">
         <is>
+          <t>isSequence(a, b, c): returns true iff a, b, c form an arithmetic sequence (b - a == c - b).</t>
+        </is>
+      </c>
+      <c r="D21" s="2" t="inlineStr">
+        <is>
           <t>T_rev_exclusion</t>
         </is>
       </c>
-      <c r="D21" s="2" t="inlineStr">
+      <c r="E21" s="2" t="inlineStr">
         <is>
           <t>(a1 ~= c2)  AND  (b1 ~= b2)  AND  (c1 ~= a2)</t>
         </is>
       </c>
-      <c r="E21" s="2" t="inlineStr">
+      <c r="F21" s="2" t="inlineStr">
         <is>
           <t>!(out2  AND  out1)</t>
         </is>
       </c>
-      <c r="F21" s="2" t="inlineStr"/>
       <c r="G21" s="2" t="inlineStr"/>
+      <c r="H21" s="2" t="inlineStr"/>
     </row>
     <row r="22">
       <c r="A22" s="2" t="inlineStr">
@@ -1062,21 +1168,26 @@
       </c>
       <c r="C22" s="2" t="inlineStr">
         <is>
+          <t>isSequence(a, b, c): returns true iff a, b, c form an arithmetic sequence (b - a == c - b).</t>
+        </is>
+      </c>
+      <c r="D22" s="2" t="inlineStr">
+        <is>
           <t>T_shift</t>
         </is>
       </c>
-      <c r="D22" s="2" t="inlineStr">
+      <c r="E22" s="2" t="inlineStr">
         <is>
           <t>((|(a1 - a2) - (b1 - b2)| &lt; eps))  AND  ((|(b1 - b2) - (c1 - c2)| &lt; eps))</t>
         </is>
       </c>
-      <c r="E22" s="2" t="inlineStr">
+      <c r="F22" s="2" t="inlineStr">
         <is>
           <t>out1 = out2</t>
         </is>
       </c>
-      <c r="F22" s="2" t="inlineStr"/>
       <c r="G22" s="2" t="inlineStr"/>
+      <c r="H22" s="2" t="inlineStr"/>
     </row>
     <row r="23">
       <c r="A23" s="2" t="inlineStr">
@@ -1091,21 +1202,26 @@
       </c>
       <c r="C23" s="2" t="inlineStr">
         <is>
+          <t>lcmSig(a, b): least common multiple of |a| and |b| (inputs sign-normalised).</t>
+        </is>
+      </c>
+      <c r="D23" s="2" t="inlineStr">
+        <is>
           <t>G_swap_negate</t>
         </is>
       </c>
-      <c r="D23" s="2" t="inlineStr">
+      <c r="E23" s="2" t="inlineStr">
         <is>
           <t>(a1 = b2)  AND  (b1 = a2)</t>
         </is>
       </c>
-      <c r="E23" s="2" t="inlineStr">
+      <c r="F23" s="2" t="inlineStr">
         <is>
           <t>out1 = out2</t>
         </is>
       </c>
-      <c r="F23" s="2" t="inlineStr"/>
       <c r="G23" s="2" t="inlineStr"/>
+      <c r="H23" s="2" t="inlineStr"/>
     </row>
     <row r="24">
       <c r="A24" s="2" t="inlineStr">
@@ -1120,21 +1236,26 @@
       </c>
       <c r="C24" s="2" t="inlineStr">
         <is>
+          <t>lcmSig(a, b): least common multiple of |a| and |b| (inputs sign-normalised).</t>
+        </is>
+      </c>
+      <c r="D24" s="2" t="inlineStr">
+        <is>
           <t>L_scale</t>
         </is>
       </c>
-      <c r="D24" s="2" t="inlineStr">
+      <c r="E24" s="2" t="inlineStr">
         <is>
           <t>(a1 = 2·a2)  AND  (b1 = 2·b2)</t>
         </is>
       </c>
-      <c r="E24" s="2" t="inlineStr">
+      <c r="F24" s="2" t="inlineStr">
         <is>
           <t>out1 = 2·out2</t>
         </is>
       </c>
-      <c r="F24" s="2" t="inlineStr"/>
       <c r="G24" s="2" t="inlineStr"/>
+      <c r="H24" s="2" t="inlineStr"/>
     </row>
     <row r="25">
       <c r="A25" s="2" t="inlineStr">
@@ -1149,21 +1270,26 @@
       </c>
       <c r="C25" s="2" t="inlineStr">
         <is>
+          <t>midpoint(a, b): arithmetic midpoint, (a + b) / 2.</t>
+        </is>
+      </c>
+      <c r="D25" s="2" t="inlineStr">
+        <is>
           <t>G_swap_negate</t>
         </is>
       </c>
-      <c r="D25" s="2" t="inlineStr">
+      <c r="E25" s="2" t="inlineStr">
         <is>
           <t>(a1 ~= b2)  AND  (b1 ~= a2)</t>
         </is>
       </c>
-      <c r="E25" s="2" t="inlineStr">
+      <c r="F25" s="2" t="inlineStr">
         <is>
           <t>out1 ~= out2</t>
         </is>
       </c>
-      <c r="F25" s="2" t="inlineStr"/>
       <c r="G25" s="2" t="inlineStr"/>
+      <c r="H25" s="2" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" s="2" t="inlineStr">
@@ -1178,21 +1304,26 @@
       </c>
       <c r="C26" s="2" t="inlineStr">
         <is>
+          <t>midpoint(a, b): arithmetic midpoint, (a + b) / 2.</t>
+        </is>
+      </c>
+      <c r="D26" s="2" t="inlineStr">
+        <is>
           <t>L_scale</t>
         </is>
       </c>
-      <c r="D26" s="2" t="inlineStr">
+      <c r="E26" s="2" t="inlineStr">
         <is>
           <t>(a1 ~= 2.0·a2)  AND  (b1 ~= 2.0·b2)</t>
         </is>
       </c>
-      <c r="E26" s="2" t="inlineStr">
+      <c r="F26" s="2" t="inlineStr">
         <is>
           <t>out1 ~= 2.0·out2</t>
         </is>
       </c>
-      <c r="F26" s="2" t="inlineStr"/>
       <c r="G26" s="2" t="inlineStr"/>
+      <c r="H26" s="2" t="inlineStr"/>
     </row>
     <row r="27">
       <c r="A27" s="2" t="inlineStr">
@@ -1207,21 +1338,26 @@
       </c>
       <c r="C27" s="2" t="inlineStr">
         <is>
+          <t>midpoint(a, b): arithmetic midpoint, (a + b) / 2.</t>
+        </is>
+      </c>
+      <c r="D27" s="2" t="inlineStr">
+        <is>
           <t>O_le_mono_in_a</t>
         </is>
       </c>
-      <c r="D27" s="2" t="inlineStr">
+      <c r="E27" s="2" t="inlineStr">
         <is>
           <t>a2 &lt;= a1  AND  (b2 ~= b1)</t>
         </is>
       </c>
-      <c r="E27" s="2" t="inlineStr">
+      <c r="F27" s="2" t="inlineStr">
         <is>
           <t>out2 &lt;= out1</t>
         </is>
       </c>
-      <c r="F27" s="2" t="inlineStr"/>
       <c r="G27" s="2" t="inlineStr"/>
+      <c r="H27" s="2" t="inlineStr"/>
     </row>
     <row r="28">
       <c r="A28" s="2" t="inlineStr">
@@ -1236,21 +1372,26 @@
       </c>
       <c r="C28" s="2" t="inlineStr">
         <is>
+          <t>midpoint(a, b): arithmetic midpoint, (a + b) / 2.</t>
+        </is>
+      </c>
+      <c r="D28" s="2" t="inlineStr">
+        <is>
           <t>T_shift</t>
         </is>
       </c>
-      <c r="D28" s="2" t="inlineStr">
+      <c r="E28" s="2" t="inlineStr">
         <is>
           <t>((a1 ~= (a2 + 1.0)))  AND  ((b1 ~= (b2 + 1.0)))</t>
         </is>
       </c>
-      <c r="E28" s="2" t="inlineStr">
+      <c r="F28" s="2" t="inlineStr">
         <is>
           <t>out1 ~= (out2 + 1.0)</t>
         </is>
       </c>
-      <c r="F28" s="2" t="inlineStr"/>
       <c r="G28" s="2" t="inlineStr"/>
+      <c r="H28" s="2" t="inlineStr"/>
     </row>
     <row r="29">
       <c r="A29" s="2" t="inlineStr">
@@ -1265,21 +1406,26 @@
       </c>
       <c r="C29" s="2" t="inlineStr">
         <is>
+          <t>powerSig(base, n): |base| raised to the power n (base sign-normalised before exponentiation).</t>
+        </is>
+      </c>
+      <c r="D29" s="2" t="inlineStr">
+        <is>
           <t>D_reciprocal_exp</t>
         </is>
       </c>
-      <c r="D29" s="2" t="inlineStr">
+      <c r="E29" s="2" t="inlineStr">
         <is>
           <t>(base1 ~= base2)  AND  base2 != 0.0  AND  n1 = -n2</t>
         </is>
       </c>
-      <c r="E29" s="2" t="inlineStr">
+      <c r="F29" s="2" t="inlineStr">
         <is>
           <t>out1 ~= (1.0 / out2)</t>
         </is>
       </c>
-      <c r="F29" s="2" t="inlineStr"/>
       <c r="G29" s="2" t="inlineStr"/>
+      <c r="H29" s="2" t="inlineStr"/>
     </row>
     <row r="30">
       <c r="A30" s="2" t="inlineStr">
@@ -1294,21 +1440,26 @@
       </c>
       <c r="C30" s="2" t="inlineStr">
         <is>
+          <t>powerSig(base, n): |base| raised to the power n (base sign-normalised before exponentiation).</t>
+        </is>
+      </c>
+      <c r="D30" s="2" t="inlineStr">
+        <is>
           <t>E_power_of_power</t>
         </is>
       </c>
-      <c r="D30" s="2" t="inlineStr">
+      <c r="E30" s="2" t="inlineStr">
         <is>
           <t>base1 ~= out2</t>
         </is>
       </c>
-      <c r="E30" s="2" t="inlineStr">
+      <c r="F30" s="2" t="inlineStr">
         <is>
           <t>out1 ~= powerSig(base2, n2·n1)</t>
         </is>
       </c>
-      <c r="F30" s="2" t="inlineStr"/>
       <c r="G30" s="2" t="inlineStr"/>
+      <c r="H30" s="2" t="inlineStr"/>
     </row>
     <row r="31">
       <c r="A31" s="2" t="inlineStr">
@@ -1323,21 +1474,26 @@
       </c>
       <c r="C31" s="2" t="inlineStr">
         <is>
+          <t>powerSig(base, n): |base| raised to the power n (base sign-normalised before exponentiation).</t>
+        </is>
+      </c>
+      <c r="D31" s="2" t="inlineStr">
+        <is>
           <t>G_odd_negate</t>
         </is>
       </c>
-      <c r="D31" s="2" t="inlineStr">
+      <c r="E31" s="2" t="inlineStr">
         <is>
           <t>(n1 = n2)  AND  ((base1 ~= (-base2)))</t>
         </is>
       </c>
-      <c r="E31" s="2" t="inlineStr">
+      <c r="F31" s="2" t="inlineStr">
         <is>
           <t>((n2 % 2 = 0)  AND  (out1 ~= out2))  OR  ((n2 % 2 != 0)  AND  ((out1 ~= (-out2))))</t>
         </is>
       </c>
-      <c r="F31" s="2" t="inlineStr"/>
       <c r="G31" s="2" t="inlineStr"/>
+      <c r="H31" s="2" t="inlineStr"/>
     </row>
     <row r="32">
       <c r="A32" s="2" t="inlineStr">
@@ -1352,21 +1508,26 @@
       </c>
       <c r="C32" s="2" t="inlineStr">
         <is>
+          <t>powerSig(base, n): |base| raised to the power n (base sign-normalised before exponentiation).</t>
+        </is>
+      </c>
+      <c r="D32" s="2" t="inlineStr">
+        <is>
           <t>L_scale_base</t>
         </is>
       </c>
-      <c r="D32" s="2" t="inlineStr">
+      <c r="E32" s="2" t="inlineStr">
         <is>
           <t>(base1 ~= 3.0·base2)  AND  (n1 = n2)</t>
         </is>
       </c>
-      <c r="E32" s="2" t="inlineStr">
+      <c r="F32" s="2" t="inlineStr">
         <is>
           <t>out1 ~= (powerSig(3.0, n2)·out2)</t>
         </is>
       </c>
-      <c r="F32" s="2" t="inlineStr"/>
       <c r="G32" s="2" t="inlineStr"/>
+      <c r="H32" s="2" t="inlineStr"/>
     </row>
     <row r="33">
       <c r="A33" s="2" t="inlineStr">
@@ -1381,21 +1542,26 @@
       </c>
       <c r="C33" s="2" t="inlineStr">
         <is>
+          <t>powerSig(base, n): |base| raised to the power n (base sign-normalised before exponentiation).</t>
+        </is>
+      </c>
+      <c r="D33" s="2" t="inlineStr">
+        <is>
           <t>T_exp_step</t>
         </is>
       </c>
-      <c r="D33" s="2" t="inlineStr">
+      <c r="E33" s="2" t="inlineStr">
         <is>
           <t>base1 = base2  AND  (n1 = (n2 + 1))</t>
         </is>
       </c>
-      <c r="E33" s="2" t="inlineStr">
+      <c r="F33" s="2" t="inlineStr">
         <is>
           <t>out1 ~= (out2·base2)</t>
         </is>
       </c>
-      <c r="F33" s="2" t="inlineStr"/>
       <c r="G33" s="2" t="inlineStr"/>
+      <c r="H33" s="2" t="inlineStr"/>
     </row>
     <row r="34">
       <c r="A34" s="2" t="inlineStr">
@@ -1410,21 +1576,26 @@
       </c>
       <c r="C34" s="2" t="inlineStr">
         <is>
+          <t>signum(x): sign of x; returns -1, 0, or +1 for x&lt;0, x=0, x&gt;0.</t>
+        </is>
+      </c>
+      <c r="D34" s="2" t="inlineStr">
+        <is>
           <t>D_reciprocal</t>
         </is>
       </c>
-      <c r="D34" s="2" t="inlineStr">
+      <c r="E34" s="2" t="inlineStr">
         <is>
           <t>x2 != 0.0  AND  (x1 ~= (1.0 / x2))</t>
         </is>
       </c>
-      <c r="E34" s="2" t="inlineStr">
+      <c r="F34" s="2" t="inlineStr">
         <is>
           <t>out1 = out2</t>
         </is>
       </c>
-      <c r="F34" s="2" t="inlineStr"/>
       <c r="G34" s="2" t="inlineStr"/>
+      <c r="H34" s="2" t="inlineStr"/>
     </row>
     <row r="35">
       <c r="A35" s="2" t="inlineStr">
@@ -1439,21 +1610,26 @@
       </c>
       <c r="C35" s="2" t="inlineStr">
         <is>
+          <t>signum(x): sign of x; returns -1, 0, or +1 for x&lt;0, x=0, x&gt;0.</t>
+        </is>
+      </c>
+      <c r="D35" s="2" t="inlineStr">
+        <is>
           <t>G_negate</t>
         </is>
       </c>
-      <c r="D35" s="2" t="inlineStr">
+      <c r="E35" s="2" t="inlineStr">
         <is>
           <t>x1 ~= (-x2)</t>
         </is>
       </c>
-      <c r="E35" s="2" t="inlineStr">
+      <c r="F35" s="2" t="inlineStr">
         <is>
           <t>out1 = - out2</t>
         </is>
       </c>
-      <c r="F35" s="2" t="inlineStr"/>
       <c r="G35" s="2" t="inlineStr"/>
+      <c r="H35" s="2" t="inlineStr"/>
     </row>
     <row r="36">
       <c r="A36" s="2" t="inlineStr">
@@ -1468,21 +1644,26 @@
       </c>
       <c r="C36" s="2" t="inlineStr">
         <is>
+          <t>signum(x): sign of x; returns -1, 0, or +1 for x&lt;0, x=0, x&gt;0.</t>
+        </is>
+      </c>
+      <c r="D36" s="2" t="inlineStr">
+        <is>
           <t>L_scale_pos</t>
         </is>
       </c>
-      <c r="D36" s="2" t="inlineStr">
+      <c r="E36" s="2" t="inlineStr">
         <is>
           <t>x1 ~= 3.0·x2</t>
         </is>
       </c>
-      <c r="E36" s="2" t="inlineStr">
+      <c r="F36" s="2" t="inlineStr">
         <is>
           <t>out1 = out2</t>
         </is>
       </c>
-      <c r="F36" s="2" t="inlineStr"/>
       <c r="G36" s="2" t="inlineStr"/>
+      <c r="H36" s="2" t="inlineStr"/>
     </row>
     <row r="37">
       <c r="A37" s="2" t="inlineStr">
@@ -1497,25 +1678,30 @@
       </c>
       <c r="C37" s="2" t="inlineStr">
         <is>
+          <t>signum(x): sign of x; returns -1, 0, or +1 for x&lt;0, x=0, x&gt;0.</t>
+        </is>
+      </c>
+      <c r="D37" s="2" t="inlineStr">
+        <is>
           <t>O_le_monotone</t>
         </is>
       </c>
-      <c r="D37" s="2" t="inlineStr">
+      <c r="E37" s="2" t="inlineStr">
         <is>
           <t>x2 &lt;= x1</t>
         </is>
       </c>
-      <c r="E37" s="2" t="inlineStr">
+      <c r="F37" s="2" t="inlineStr">
         <is>
           <t>out2 &lt;= out1</t>
         </is>
       </c>
-      <c r="F37" s="2" t="inlineStr"/>
       <c r="G37" s="2" t="inlineStr"/>
+      <c r="H37" s="2" t="inlineStr"/>
     </row>
   </sheetData>
   <dataValidations count="1">
-    <dataValidation sqref="F2:F37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Choose one of: a b c d e f g h i j orphan" promptTitle="MR family" prompt="Pick ONE family a-j (or orphan). See CODEBOOK." type="list">
+    <dataValidation sqref="G2:G37" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" errorTitle="Invalid" error="Choose one of: a b c d e f g h i j orphan" promptTitle="MR family" prompt="Pick ONE family a-j (or orphan). See CODEBOOK." type="list">
       <formula1>"a,b,c,d,e,f,g,h,i,j,orphan"</formula1>
     </dataValidation>
   </dataValidations>
